--- a/pre-week-2/homework1.xlsx
+++ b/pre-week-2/homework1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danaitberhane\Documents\DataAnalytics\pre-week-1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danaitberhane\Documents\DataAnalytics\pre-week-2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D497296B-77F6-46E4-9CFF-8C07C1361785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94A61F59-5CE4-4B14-96EE-7846D8287C1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BAB12EC4-57B1-4808-9497-E08C684D3C18}"/>
+    <workbookView xWindow="2580" yWindow="1360" windowWidth="14400" windowHeight="8170" xr2:uid="{6457ADA6-6F5A-4948-A9CB-F2C445CF0DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,86 +35,12 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>Dataset</t>
-  </si>
-  <si>
-    <t>Student 2</t>
-  </si>
-  <si>
-    <t>Student 1</t>
-  </si>
-  <si>
-    <t>Student 4</t>
-  </si>
-  <si>
-    <t>Student 3</t>
-  </si>
-  <si>
-    <t>Student 5</t>
-  </si>
-  <si>
-    <t>Student 7</t>
-  </si>
-  <si>
-    <t>Student 8</t>
-  </si>
-  <si>
-    <t>Student 9</t>
-  </si>
-  <si>
-    <t>Student 10</t>
-  </si>
-  <si>
-    <t>Student 6</t>
-  </si>
-  <si>
-    <t>Student</t>
-  </si>
-  <si>
-    <t>Score</t>
-  </si>
-  <si>
-    <t>Descriptive statistics</t>
-  </si>
-  <si>
-    <t>Maximum</t>
-  </si>
-  <si>
-    <t>Minimum</t>
-  </si>
-  <si>
-    <t>Range</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <t>Standard Deviation</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -157,6 +83,86 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{580EB93D-2A60-15A7-A07B-56A03BA31B95}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1162050" y="628650"/>
+          <a:ext cx="6851650" cy="2063750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100"/>
+            <a:t>The</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" baseline="0"/>
+            <a:t> average monthley sales is about 49.42 and the median is 47.5 which shows the most stores performs around the same level. The data is somewhat spread out since the range is 29 and the standard devation is about 7.31. Most stores are close to the averages but one value(72) is much higher than the rest and affects the results by increasing the avergae. Overall most stores perform pretty similiarly but there are some difference. Knowing things like store location, size, and how many cusomers they get would help explain why some stores do bettter than others.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -475,157 +481,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6C1C511-D176-4ED8-BFB6-EC484A338742}">
-  <dimension ref="A1:E12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CB6155C-8F86-4534-937E-ED3833598427}">
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="20.1796875" customWidth="1"/>
-    <col min="3" max="3" width="4.81640625" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" customWidth="1"/>
-    <col min="6" max="6" width="1.08984375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>75</v>
-      </c>
-      <c r="D5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
-        <v>78.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>80</v>
-      </c>
-      <c r="D6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6">
-        <v>77.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>85</v>
-      </c>
-      <c r="D7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
-        <v>90</v>
-      </c>
-      <c r="D8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8">
-        <v>8.9600000000000009</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>70</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>